--- a/data/EquipSlot.xlsx
+++ b/data/EquipSlot.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,6 +425,11 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>equip_kind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
         </is>
       </c>
     </row>
@@ -442,6 +447,11 @@
           <t>该槽位接受的装备部位;没在本表里出现的槽位不接受任何东西</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>槽位显示名(下发客户端,空槽显示它);可留空</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -465,6 +475,58 @@
       </c>
       <c r="B8" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>帽子</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
       </c>
     </row>
   </sheetData>
